--- a/data/g_vs_random_1_checkers.xlsx
+++ b/data/g_vs_random_1_checkers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,6 +1061,226 @@
         <v>23.855</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B58" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>23.929</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B59" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>23.656</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B60" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="C60" t="n">
+        <v>24.512</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B61" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>23.925</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B62" t="n">
+        <v>52</v>
+      </c>
+      <c r="C62" t="n">
+        <v>24.31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B64" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="C64" t="n">
+        <v>23.306</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B65" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C65" t="n">
+        <v>24.085</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B66" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>23.609</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B67" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>24.484</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B68" t="n">
+        <v>54</v>
+      </c>
+      <c r="C68" t="n">
+        <v>24.171</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B69" t="n">
+        <v>52</v>
+      </c>
+      <c r="C69" t="n">
+        <v>23.967</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B70" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>23.809</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B71" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>24.195</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B72" t="n">
+        <v>52</v>
+      </c>
+      <c r="C72" t="n">
+        <v>24.334</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B73" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>24.409</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B74" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>24.118</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B75" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>24.217</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B76" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>24.084</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B77" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>24.452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/g_vs_random_1_checkers.xlsx
+++ b/data/g_vs_random_1_checkers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,6 +1281,116 @@
         <v>24.452</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B78" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="C78" t="n">
+        <v>23.892</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B79" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="C79" t="n">
+        <v>24.543</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B80" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="C80" t="n">
+        <v>24.466</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B81" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="C81" t="n">
+        <v>24.614</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B82" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="C82" t="n">
+        <v>23.74</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B83" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="C83" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B84" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>23.562</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B85" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>23.702</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B86" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>23.744</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B87" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="C87" t="n">
+        <v>23.603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/g_vs_random_1_checkers.xlsx
+++ b/data/g_vs_random_1_checkers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,6 +1391,83 @@
         <v>23.603</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B88" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="C88" t="n">
+        <v>24.467</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B89" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C89" t="n">
+        <v>23.993</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B90" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="C90" t="n">
+        <v>24.063</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B91" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C91" t="n">
+        <v>23.814</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B92" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C92" t="n">
+        <v>23.584</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B93" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C93" t="n">
+        <v>23.581</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B94" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C94" t="n">
+        <v>24.009</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
